--- a/data_execl/base_data/MultiLanguage.xlsx
+++ b/data_execl/base_data/MultiLanguage.xlsx
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>日文</t>
+          <t>日本語</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
